--- a/test/excel/win/parts/struct-held/copy-to-t.xlsx
+++ b/test/excel/win/parts/struct-held/copy-to-t.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xlcalc\work\parts-struct-held-45796-1\out\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xlcalc\work\parts-struct-held-30311-1\out\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EEED97CF-A36E-464E-A4A4-425DBEFBED94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3128B29A-110D-4921-9E75-710680EB7FE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -560,8 +560,8 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" location="S!B5" display="to B5" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="D4" location="S!A1" display="to A1" xr:uid="{FBED1053-664B-41DA-97FC-27C42CD87CBD}"/>
-    <hyperlink ref="E5" location="'T'!A1" display="to T" xr:uid="{B51F9637-BF7D-4676-8776-BD51F7C8FA98}"/>
+    <hyperlink ref="D4" location="S!A1" display="to A1" xr:uid="{5AEB5313-C9BD-4F82-BAB3-E606EB370244}"/>
+    <hyperlink ref="E5" location="'T'!A1" display="to T" xr:uid="{A8E5A4C4-FF95-4E15-B083-1DE039026863}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
